--- a/Master/7273r00/7273r00 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/7273r00/7273r00 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1434,150 +1434,150 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>2.129</v>
+        <v>1.237</v>
       </c>
       <c r="B50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="D50" s="7" t="n">
-        <v>6.8624</v>
+        <v>6.8283</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>-1.6019</v>
+        <v>-3.7277</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.0146</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>5.129</v>
+        <v>2.129</v>
       </c>
       <c r="B51" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>6.8627</v>
+        <v>6.8624</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-1.4774</v>
+        <v>-1.6019</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.0138</v>
+        <v>0.0146</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>6.13</v>
+        <v>5.129</v>
       </c>
       <c r="B52" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>6.9672</v>
+        <v>6.8627</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>-1.6764</v>
+        <v>-1.4774</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.0123</v>
+        <v>0.0138</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>3.13</v>
+        <v>6.13</v>
       </c>
       <c r="B53" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>6.9673</v>
+        <v>6.9672</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-1.802</v>
+        <v>-1.6764</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>0.0117</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>1.131</v>
+        <v>3.13</v>
       </c>
       <c r="B54" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C54" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>7.0541</v>
+        <v>6.9673</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>-2.132</v>
+        <v>-1.802</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.0098</v>
+        <v>0.0117</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>4.131</v>
+        <v>1.131</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C55" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>7.0542</v>
+        <v>7.0541</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-2.0071</v>
+        <v>-2.132</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>0.0097</v>
+        <v>0.0098</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>2.132</v>
+        <v>4.131</v>
       </c>
       <c r="B56" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C56" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>7.124</v>
+        <v>7.0542</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>-2.3408</v>
+        <v>-2.0071</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>5.132</v>
+        <v>2.132</v>
       </c>
       <c r="B57" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C57" s="6" t="n">
         <v>1</v>
@@ -1586,87 +1586,87 @@
         <v>7.124</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-2.2162</v>
+        <v>-2.3408</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.0075</v>
+        <v>0.007900000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>3.133</v>
+        <v>5.132</v>
       </c>
       <c r="B58" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C58" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>7.1836</v>
+        <v>7.124</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>-2.5396</v>
+        <v>-2.2162</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>0.007</v>
+        <v>0.0075</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>6.133</v>
+        <v>3.133</v>
       </c>
       <c r="B59" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>7.1837</v>
+        <v>7.1836</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-2.4145</v>
+        <v>-2.5396</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>0.0074</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>1.134</v>
+        <v>6.133</v>
       </c>
       <c r="B60" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C60" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>7.2376</v>
+        <v>7.1837</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>-2.8682</v>
+        <v>-2.4145</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.0063</v>
+        <v>0.0074</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>4.134</v>
+        <v>1.134</v>
       </c>
       <c r="B61" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C61" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>7.2378</v>
+        <v>7.2376</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-2.7436</v>
+        <v>-2.8682</v>
       </c>
       <c r="F61" s="7" t="n">
         <v>0.0063</v>
@@ -1674,30 +1674,30 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>2.135</v>
+        <v>4.134</v>
       </c>
       <c r="B62" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C62" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>7.284</v>
+        <v>7.2378</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>-3.0828</v>
+        <v>-2.7436</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>0.0054</v>
+        <v>0.0063</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>5.135</v>
+        <v>2.135</v>
       </c>
       <c r="B63" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C63" s="6" t="n">
         <v>1</v>
@@ -1706,30 +1706,50 @@
         <v>7.284</v>
       </c>
       <c r="E63" s="7" t="n">
+        <v>-3.0828</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>0.0054</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>5.135</v>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>7.284</v>
+      </c>
+      <c r="E64" s="7" t="n">
         <v>-2.9584</v>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F64" s="7" t="n">
         <v>0.0051</v>
       </c>
     </row>
-    <row r="65">
-      <c r="E65" s="8" t="inlineStr">
+    <row r="66">
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F65" s="9" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="E66" s="8" t="inlineStr">
+      <c r="F66" s="9" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F66" s="10" t="n">
-        <v>1.8169</v>
+      <c r="F67" s="10" t="n">
+        <v>1.817</v>
       </c>
     </row>
   </sheetData>
